--- a/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_thi_diem_4dang_bien_the.xlsx
+++ b/data/questions/mu_logarit_extraction/bien_the/Mu_Logarit_thi_diem_4dang_bien_the.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,11 +983,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>p124_q21</t>
+          <t>p006_q14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
+        <is>
+          <t>Giải bất phương trình $\log_2(3x-1) &gt; 3$.
+A. $x &gt; 3$.
+B. $\dfrac{1}{3} &lt; x &lt; 3$.
+C. $x &lt; 3$.
+D. $x &gt; \dfrac{10}{3}$.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A. x &gt; 3</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Đạt (câu gốc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Câu gốc</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>p124_q21</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Tập nghiệm của bất phương trình $\log(x-2)&gt;0$ là
 A. $(2;3)$.
@@ -996,39 +1037,39 @@
 D. $(12;+\infty)$.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>C. $(3;+\infty)$.</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Đạt (câu gốc)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>D53</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Câu gốc</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>p221_q08</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Tập nghiệm của bất phương trình $\log_3(2x)&gt;2$ là
 A. $(0;4)$.
@@ -1037,39 +1078,39 @@
 D. $(4;+\infty)$.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>B. $\left(\dfrac92;+\infty\right)$</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Đạt (câu gốc)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>D53</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Câu gốc</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>p236_q12</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Tập nghiệm của bất phương trình $\log_5(x+1)&gt;2$ là
 A. $(9;+\infty)$.
@@ -1078,43 +1119,43 @@
 D. $(24;+\infty)$.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>D. $(24;+\infty)$</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Đạt (câu gốc)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>p006_q12</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{5}(x+3)=3$ là
 A. $x=123$.
@@ -1123,47 +1164,47 @@
 D. $x=12$.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>C. $x=122$.</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Điều kiện: $x+3&gt;0$. Ta có $\log_{5}(x+3)=3 \Leftrightarrow x+3=5^{3}=125 \Leftrightarrow x=122$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>p006_q12</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{2}(x-4)=4$ là
 A. $x=21$.
@@ -1172,47 +1213,47 @@
 D. $x=12$.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>B. $x=20$.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Điều kiện: $x-4&gt;0$. Ta có $\log_{2}(x-4)=4 \Leftrightarrow x-4=2^{4}=16 \Leftrightarrow x=20$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>p006_q12</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{7}(3x-5)=4$ là
 A. $x=802$.
@@ -1221,47 +1262,47 @@
 D. $x=11$.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>A. $x=802$.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-5&gt;0$. Ta có $\log_{7}(3x-5)=4 \Leftrightarrow 3x-5=7^{4}=2401 \Leftrightarrow x=802$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>p006_q12</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{6}(3x-3)=2$ là
 A. $x=39$.
@@ -1270,47 +1311,47 @@
 D. $x=5$.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>C. $x=13$.</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-3&gt;0$. Ta có $\log_{6}(3x-3)=2 \Leftrightarrow 3x-3=6^{2}=36 \Leftrightarrow x=13$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>p006_q12</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{7}(2x-2)=2$ là
 A. $x=8$.
@@ -1319,47 +1360,47 @@
 D. $x=\dfrac{51}{2}$.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>D. $x=\dfrac{51}{2}$.</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Điều kiện: $2x-2&gt;0$. Ta có $\log_{7}(2x-2)=2 \Leftrightarrow 2x-2=7^{2}=49 \Leftrightarrow x=\dfrac{51}{2}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>p006_q12</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{2}(3x-2)=1$ là
 A. $x=\dfrac{7}{3}$.
@@ -1368,47 +1409,47 @@
 D. $x=\dfrac{4}{3}$.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>D. $x=\dfrac{4}{3}$.</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-2&gt;0$. Ta có $\log_{2}(3x-2)=1 \Leftrightarrow 3x-2=2^{1}=2 \Leftrightarrow x=\dfrac{4}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>p079_q06</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{2}(x-7)=4$ là
 A. $x=15$.
@@ -1417,47 +1458,47 @@
 D. $x=11$.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>C. $x=23$.</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Điều kiện: $x-7&gt;0$. Ta có $\log_{2}(x-7)=4 \Leftrightarrow x-7=2^{4}=16 \Leftrightarrow x=23$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>p079_q06</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{3}(x+2)=4$ là
 A. $x=79$.
@@ -1466,47 +1507,47 @@
 D. $x=10$.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>A. $x=79$.</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Điều kiện: $x+2&gt;0$. Ta có $\log_{3}(x+2)=4 \Leftrightarrow x+2=3^{4}=81 \Leftrightarrow x=79$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>p079_q06</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{6}(2x-8)=1$ là
 A. $x=8$.
@@ -1515,47 +1556,47 @@
 D. $x=7$.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>D. $x=7$.</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Điều kiện: $2x-8&gt;0$. Ta có $\log_{6}(2x-8)=1 \Leftrightarrow 2x-8=6^{1}=6 \Leftrightarrow x=7$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>p079_q06</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{2}(2x+4)=2$ là
 A. $x=-1$.
@@ -1564,47 +1605,47 @@
 D. $x=2$.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>C. $x=0$.</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Điều kiện: $2x+4&gt;0$. Ta có $\log_{2}(2x+4)=2 \Leftrightarrow 2x+4=2^{2}=4 \Leftrightarrow x=0$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>p079_q06</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{2}(3x)=1$ là
 A. $x=\dfrac{5}{3}$.
@@ -1613,47 +1654,47 @@
 D. $x=\dfrac{1}{3}$.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>B. $x=\dfrac{2}{3}$.</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Điều kiện: $3x&gt;0$. Ta có $\log_{2}(3x)=1 \Leftrightarrow 3x=2^{1}=2 \Leftrightarrow x=\dfrac{2}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>p079_q06</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{6}(3x-5)=3$ là
 A. $x=\dfrac{221}{3}$.
@@ -1662,47 +1703,47 @@
 D. $x=\dfrac{8}{3}$.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>A. $x=\dfrac{221}{3}$.</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-5&gt;0$. Ta có $\log_{6}(3x-5)=3 \Leftrightarrow 3x-5=6^{3}=216 \Leftrightarrow x=\dfrac{221}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>p109_q10</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{6}(x-2)=2$ là
 A. $x=14$.
@@ -1711,47 +1752,47 @@
 D. $x=38$.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>D. $x=38$.</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Điều kiện: $x-2&gt;0$. Ta có $\log_{6}(x-2)=2 \Leftrightarrow x-2=6^{2}=36 \Leftrightarrow x=38$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>p109_q10</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{3}(x+6)=2$ là
 A. $x=-4$.
@@ -1760,47 +1801,47 @@
 D. $x=3$.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>D. $x=3$.</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Điều kiện: $x+6&gt;0$. Ta có $\log_{3}(x+6)=2 \Leftrightarrow x+6=3^{2}=9 \Leftrightarrow x=3$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>p109_q10</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{6}(3x)=1$ là
 A. $x=3$.
@@ -1809,47 +1850,47 @@
 D. $x=2$.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>D. $x=2$.</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Điều kiện: $3x&gt;0$. Ta có $\log_{6}(3x)=1 \Leftrightarrow 3x=6^{1}=6 \Leftrightarrow x=2$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>p109_q10</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{2}(3x-7)=1$ là
 A. $x=9$.
@@ -1858,47 +1899,47 @@
 D. $x=3$.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>D. $x=3$.</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-7&gt;0$. Ta có $\log_{2}(3x-7)=1 \Leftrightarrow 3x-7=2^{1}=2 \Leftrightarrow x=3$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>p109_q10</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{5}(3x+6)=2$ là
 A. $x=\dfrac{4}{3}$.
@@ -1907,47 +1948,47 @@
 D. $x=19$.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>C. $x=\dfrac{19}{3}$.</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Điều kiện: $3x+6&gt;0$. Ta có $\log_{5}(3x+6)=2 \Leftrightarrow 3x+6=5^{2}=25 \Leftrightarrow x=\dfrac{19}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>p109_q10</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{6}(3x-5)=4$ là
 A. $x=\dfrac{1301}{3}$.
@@ -1956,47 +1997,47 @@
 D. $x=1301$.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>A. $x=\dfrac{1301}{3}$.</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-5&gt;0$. Ta có $\log_{6}(3x-5)=4 \Leftrightarrow 3x-5=6^{4}=1296 \Leftrightarrow x=\dfrac{1301}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>p191_q08</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{5}(x-2)=4$ là
 A. $x=627$.
@@ -2005,47 +2046,47 @@
 D. $x=22$.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>A. $x=627$.</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>Điều kiện: $x-2&gt;0$. Ta có $\log_{5}(x-2)=4 \Leftrightarrow x-2=5^{4}=625 \Leftrightarrow x=627$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>p191_q08</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{5}(x+3)=1$ là
 A. $x=-2$.
@@ -2054,47 +2095,47 @@
 D. $x=2$.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>D. $x=2$.</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Điều kiện: $x+3&gt;0$. Ta có $\log_{5}(x+3)=1 \Leftrightarrow x+3=5^{1}=5 \Leftrightarrow x=2$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>p191_q08</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{4}(2x+8)=1$ là
 A. $x=- \dfrac{7}{2}$.
@@ -2103,47 +2144,47 @@
 D. $x=-2$.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>D. $x=-2$.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Điều kiện: $2x+8&gt;0$. Ta có $\log_{4}(2x+8)=1 \Leftrightarrow 2x+8=4^{1}=4 \Leftrightarrow x=-2$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>p191_q08</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{4}(3x-5)=3$ là
 A. $x=23$.
@@ -2152,47 +2193,47 @@
 D. $x=69$.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>A. $x=23$.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-5&gt;0$. Ta có $\log_{4}(3x-5)=3 \Leftrightarrow 3x-5=4^{3}=64 \Leftrightarrow x=23$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>p191_q08</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{5}(3x-3)=2$ là
 A. $x=\dfrac{5}{3}$.
@@ -2201,47 +2242,47 @@
 D. $x=\dfrac{28}{3}$.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>D. $x=\dfrac{28}{3}$.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-3&gt;0$. Ta có $\log_{5}(3x-3)=2 \Leftrightarrow 3x-3=5^{2}=25 \Leftrightarrow x=\dfrac{28}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>p191_q08</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{4}(3x+6)=2$ là
 A. $x=\dfrac{2}{3}$.
@@ -2250,47 +2291,47 @@
 D. $x=- \dfrac{4}{3}$.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>B. $x=\dfrac{10}{3}$.</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Điều kiện: $3x+6&gt;0$. Ta có $\log_{4}(3x+6)=2 \Leftrightarrow 3x+6=4^{2}=16 \Leftrightarrow x=\dfrac{10}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>p210_q27</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{5}(x+8)=2$ là
 A. $x=2$.
@@ -2299,47 +2340,47 @@
 D. $x=-6$.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>C. $x=17$.</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Điều kiện: $x+8&gt;0$. Ta có $\log_{5}(x+8)=2 \Leftrightarrow x+8=5^{2}=25 \Leftrightarrow x=17$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>p210_q27</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{3}(x-8)=2$ là
 A. $x=18$.
@@ -2348,47 +2389,47 @@
 D. $x=17$.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>D. $x=17$.</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Điều kiện: $x-8&gt;0$. Ta có $\log_{3}(x-8)=2 \Leftrightarrow x-8=3^{2}=9 \Leftrightarrow x=17$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>p210_q27</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{7}(2x-5)=1$ là
 A. $x=7$.
@@ -2397,47 +2438,47 @@
 D. $x=6$.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>D. $x=6$.</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Điều kiện: $2x-5&gt;0$. Ta có $\log_{7}(2x-5)=1 \Leftrightarrow 2x-5=7^{1}=7 \Leftrightarrow x=6$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>p210_q27</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{3}(2x-7)=3$ là
 A. $x=17$.
@@ -2446,47 +2487,47 @@
 D. $x=34$.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>A. $x=17$.</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>Điều kiện: $2x-7&gt;0$. Ta có $\log_{3}(2x-7)=3 \Leftrightarrow 2x-7=3^{3}=27 \Leftrightarrow x=17$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>p210_q27</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{5}(3x-6)=1$ là
 A. $x=11$.
@@ -2495,47 +2536,47 @@
 D. $x=\dfrac{11}{3}$.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>D. $x=\dfrac{11}{3}$.</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Điều kiện: $3x-6&gt;0$. Ta có $\log_{5}(3x-6)=1 \Leftrightarrow 3x-6=5^{1}=5 \Leftrightarrow x=\dfrac{11}{3}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>D01</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>p210_q27</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $\log_{4}(2x-3)=1$ là
 A. $x=\dfrac{7}{2}$.
@@ -2544,47 +2585,47 @@
 D. $x=\dfrac{9}{2}$.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>A. $x=\dfrac{7}{2}$.</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>Điều kiện: $2x-3&gt;0$. Ta có $\log_{4}(2x-3)=1 \Leftrightarrow 2x-3=4^{1}=4 \Leftrightarrow x=\dfrac{7}{2}$ (thỏa điều kiện).</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>p020_q13</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{x+6}=625$ là
 A. $x=-2$.
@@ -2593,47 +2634,47 @@
 D. $x=10$.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>A. $x=-2$.</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Ta có $5^{x+6}=625=5^{4} \Leftrightarrow x+6=4 \Leftrightarrow x=-2$.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>p020_q13</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $4^{x+3}=16$ là
 A. $x=0$.
@@ -2642,47 +2683,47 @@
 D. $x=13$.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>B. $x=-1$.</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Ta có $4^{x+3}=16=4^{2} \Leftrightarrow x+3=2 \Leftrightarrow x=-1$.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>p020_q13</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{2x+4}=25$ là
 A. $x=-3$.
@@ -2691,47 +2732,47 @@
 D. $x=3$.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>B. $x=-1$.</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Ta có $5^{2x+4}=25=5^{2} \Leftrightarrow 2x+4=2 \Leftrightarrow x=-1$.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>p020_q13</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $2^{2x+5}=2$ là
 A. $x=- \dfrac{9}{2}$.
@@ -2740,47 +2781,47 @@
 D. $x=-2$.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>D. $x=-2$.</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Ta có $2^{2x+5}=2=2^{1} \Leftrightarrow 2x+5=1 \Leftrightarrow x=-2$.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>p020_q13</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $3^{3x+5}=3$ là
 A. $x=- \dfrac{14}{3}$.
@@ -2789,47 +2830,47 @@
 D. $x=2$.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>B. $x=- \dfrac{4}{3}$.</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Ta có $3^{3x+5}=3=3^{1} \Leftrightarrow 3x+5=1 \Leftrightarrow x=- \dfrac{4}{3}$.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>p020_q13</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{2x-1}=25$ là
 A. $x=\dfrac{1}{2}$.
@@ -2838,47 +2879,47 @@
 D. $x=2$.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>B. $x=\dfrac{3}{2}$.</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Ta có $5^{2x-1}=25=5^{2} \Leftrightarrow 2x-1=2 \Leftrightarrow x=\dfrac{3}{2}$.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>p093_q03</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $2^{x+6}=2$ là
 A. $x=-3$.
@@ -2887,47 +2928,47 @@
 D. $x=-4$.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>C. $x=-5$.</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Ta có $2^{x+6}=2=2^{1} \Leftrightarrow x+6=1 \Leftrightarrow x=-5$.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>p093_q03</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $2^{x+3}=4$ là
 A. $x=5$.
@@ -2936,47 +2977,47 @@
 D. $x=-1$.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>D. $x=-1$.</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Ta có $2^{x+3}=4=2^{2} \Leftrightarrow x+3=2 \Leftrightarrow x=-1$.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>p093_q03</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{3x-2}=5$ là
 A. $x=\dfrac{10}{3}$.
@@ -2985,47 +3026,47 @@
 D. $x=1$.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>D. $x=1$.</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Ta có $5^{3x-2}=5=5^{1} \Leftrightarrow 3x-2=1 \Leftrightarrow x=1$.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>p093_q03</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $3^{2x+2}=9$ là
 A. $x=-1$.
@@ -3034,47 +3075,47 @@
 D. $x=0$.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>D. $x=0$.</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Ta có $3^{2x+2}=9=3^{2} \Leftrightarrow 2x+2=2 \Leftrightarrow x=0$.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>p093_q03</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{2x-4}=125$ là
 A. $x=\dfrac{129}{2}$.
@@ -3083,47 +3124,47 @@
 D. $x=\dfrac{7}{2}$.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>D. $x=\dfrac{7}{2}$.</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Ta có $5^{2x-4}=125=5^{3} \Leftrightarrow 2x-4=3 \Leftrightarrow x=\dfrac{7}{2}$.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>p093_q03</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{3x+6}=5$ là
 A. $x=- \dfrac{1}{3}$.
@@ -3132,47 +3173,47 @@
 D. $x=- \dfrac{17}{3}$.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>C. $x=- \dfrac{5}{3}$.</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Ta có $5^{3x+6}=5=5^{1} \Leftrightarrow 3x+6=1 \Leftrightarrow x=- \dfrac{5}{3}$.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>p172_q13</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $2^{x+6}=2$ là
 A. $x=7$.
@@ -3181,47 +3222,47 @@
 D. $x=-5$.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>D. $x=-5$.</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Ta có $2^{x+6}=2=2^{1} \Leftrightarrow x+6=1 \Leftrightarrow x=-5$.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>p172_q13</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $4^{x+3}=4$ là
 A. $x=-1$.
@@ -3230,47 +3271,47 @@
 D. $x=-2$.</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>D. $x=-2$.</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Ta có $4^{x+3}=4=4^{1} \Leftrightarrow x+3=1 \Leftrightarrow x=-2$.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>p172_q13</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $2^{2x-1}=8$ là
 A. $x=\dfrac{9}{2}$.
@@ -3279,47 +3320,47 @@
 D. $x=\dfrac{5}{2}$.</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>B. $x=2$.</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Ta có $2^{2x-1}=8=2^{3} \Leftrightarrow 2x-1=3 \Leftrightarrow x=2$.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>p172_q13</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $4^{2x+1}=4$ là
 A. $x=\dfrac{3}{2}$.
@@ -3328,47 +3369,47 @@
 D. $x=0$.</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>D. $x=0$.</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Ta có $4^{2x+1}=4=4^{1} \Leftrightarrow 2x+1=1 \Leftrightarrow x=0$.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>p172_q13</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $4^{3x+5}=256$ là
 A. $x=3$.
@@ -3377,47 +3418,47 @@
 D. $x=- \dfrac{11}{3}$.</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>B. $x=- \dfrac{1}{3}$.</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>Ta có $4^{3x+5}=256=4^{4} \Leftrightarrow 3x+5=4 \Leftrightarrow x=- \dfrac{1}{3}$.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>p172_q13</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $4^{3x+3}=4$ là
 A. $x=\dfrac{4}{3}$.
@@ -3426,47 +3467,47 @@
 D. $x=- \dfrac{2}{3}$.</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>D. $x=- \dfrac{2}{3}$.</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Ta có $4^{3x+3}=4=4^{1} \Leftrightarrow 3x+3=1 \Leftrightarrow x=- \dfrac{2}{3}$.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>p192_q13</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $2^{x-2}=8$ là
 A. $x=5$.
@@ -3475,47 +3516,47 @@
 D. $x=10$.</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>A. $x=5$.</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Ta có $2^{x-2}=8=2^{3} \Leftrightarrow x-2=3 \Leftrightarrow x=5$.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>p192_q13</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>he_so_x_bang_1</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{x+5}=25$ là
 A. $x=-3$.
@@ -3524,47 +3565,47 @@
 D. $x=20$.</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>A. $x=-3$.</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Ta có $5^{x+5}=25=5^{2} \Leftrightarrow x+5=2 \Leftrightarrow x=-3$.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>p192_q13</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{2x+2}=625$ là
 A. $x=1$.
@@ -3573,47 +3614,47 @@
 D. $x=0$.</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>A. $x=1$.</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Ta có $5^{2x+2}=625=5^{4} \Leftrightarrow 2x+2=4 \Leftrightarrow x=1$.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" t="inlineStr">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>p192_q13</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $5^{3x-5}=5$ là
 A. $x=\dfrac{16}{3}$.
@@ -3622,47 +3663,47 @@
 D. $x=\dfrac{10}{3}$.</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>B. $x=2$.</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>Ta có $5^{3x-5}=5=5^{1} \Leftrightarrow 3x-5=1 \Leftrightarrow x=2$.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>p192_q13</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $4^{3x+2}=4$ là
 A. $x=\dfrac{2}{3}$.
@@ -3671,47 +3712,47 @@
 D. $x=- \dfrac{1}{3}$.</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>D. $x=- \dfrac{1}{3}$.</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>Ta có $4^{3x+2}=4=4^{1} \Leftrightarrow 3x+2=1 \Leftrightarrow x=- \dfrac{1}{3}$.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>D12</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>p192_q13</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Nghiệm của phương trình $2^{2x-4}=2$ là
 A. $x=3$.
@@ -3720,47 +3761,47 @@
 D. $x=- \dfrac{3}{2}$.</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>C. $x=\dfrac{5}{2}$.</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>Ta có $2^{2x-4}=2=2^{1} \Leftrightarrow 2x-4=1 \Leftrightarrow x=\dfrac{5}{2}$.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" t="inlineStr">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>p031_q02</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>co_so_nho</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{2} x$ là
 A. $y'=\dfrac{1}{x\ln 2}$.
@@ -3769,47 +3810,47 @@
 D. $y'=\dfrac{1}{2x}$.</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 2}$.</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=2$, ta có $y'=\dfrac{1}{x\ln 2}$.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>p031_q02</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>co_so_nho</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{3} x$ là
 A. $y'=\dfrac{1}{3x}$.
@@ -3818,47 +3859,47 @@
 D. $y'=\dfrac{1}{x}$.</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>C. $y'=\dfrac{1}{x\ln 3}$.</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=3$, ta có $y'=\dfrac{1}{x\ln 3}$.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" t="inlineStr">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>p031_q02</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>co_so_trung_binh</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{4} x$ là
 A. $y'=\dfrac{1}{x\ln 4}$.
@@ -3867,47 +3908,47 @@
 D. $y'=\dfrac{\ln 4}{x}$.</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 4}$.</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=4$, ta có $y'=\dfrac{1}{x\ln 4}$.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>p031_q02</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>co_so_trung_binh</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{6} x$ là
 A. $y'=\dfrac{1}{x\ln 6}$.
@@ -3916,47 +3957,47 @@
 D. $y'=\dfrac{\ln 6}{x}$.</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 6}$.</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=6$, ta có $y'=\dfrac{1}{x\ln 6}$.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>p031_q02</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>co_so_lon</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=log x$ là
 A. $y'=\dfrac{1}{x\ln 10}$.
@@ -3965,47 +4006,47 @@
 D. $y'=\dfrac{\ln 10}{x}$.</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 10}$.</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=10$, ta có $y'=\dfrac{1}{x\ln 10}$.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>p031_q02</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>co_so_lon</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{9} x$ là
 A. $y'=\dfrac{1}{9x}$.
@@ -4014,47 +4055,47 @@
 D. $y'=\dfrac{1}{x}$.</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>B. $y'=\dfrac{1}{x\ln 9}$.</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=9$, ta có $y'=\dfrac{1}{x\ln 9}$.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>p111_q22</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>co_so_nho</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{3} x$ là
 A. $y'=\dfrac{1}{3x}$.
@@ -4063,47 +4104,47 @@
 D. $y'=\dfrac{1}{x\ln 3}$.</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>D. $y'=\dfrac{1}{x\ln 3}$.</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=3$, ta có $y'=\dfrac{1}{x\ln 3}$.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>p111_q22</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>co_so_nho</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{2} x$ là
 A. $y'=\dfrac{\ln 2}{x}$.
@@ -4112,47 +4153,47 @@
 D. $y'=\dfrac{1}{x}$.</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>B. $y'=\dfrac{1}{x\ln 2}$.</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=2$, ta có $y'=\dfrac{1}{x\ln 2}$.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>p111_q22</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>co_so_trung_binh</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{6} x$ là
 A. $y'=\dfrac{1}{6x}$.
@@ -4161,47 +4202,47 @@
 D. $y'=\dfrac{\ln 6}{x}$.</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>B. $y'=\dfrac{1}{x\ln 6}$.</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=6$, ta có $y'=\dfrac{1}{x\ln 6}$.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>p111_q22</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>co_so_trung_binh</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{5} x$ là
 A. $y'=\dfrac{1}{x\ln 5}$.
@@ -4210,47 +4251,47 @@
 D. $y'=\dfrac{1}{x}$.</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 5}$.</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=5$, ta có $y'=\dfrac{1}{x\ln 5}$.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
         <is>
           <t>p111_q22</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>co_so_lon</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=log x$ là
 A. $y'=\dfrac{1}{x\ln 10}$.
@@ -4259,47 +4300,47 @@
 D. $y'=\dfrac{1}{x}$.</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 10}$.</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=10$, ta có $y'=\dfrac{1}{x\ln 10}$.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" t="inlineStr">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>p111_q22</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>co_so_lon</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{11} x$ là
 A. $y'=\dfrac{1}{x\ln 11}$.
@@ -4308,47 +4349,47 @@
 D. $y'=\dfrac{1}{x}$.</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 11}$.</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=11$, ta có $y'=\dfrac{1}{x\ln 11}$.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" t="inlineStr">
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>p121_q02</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>co_so_nho</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{2} x$ là
 A. $y'=\dfrac{1}{x\ln 2}$.
@@ -4357,47 +4398,47 @@
 D. $y'=\dfrac{1}{2x}$.</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 2}$.</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=2$, ta có $y'=\dfrac{1}{x\ln 2}$.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" t="inlineStr">
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>p121_q02</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>co_so_nho</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{3} x$ là
 A. $y'=\dfrac{1}{x\ln 3}$.
@@ -4406,47 +4447,47 @@
 D. $y'=\dfrac{\ln 3}{x}$.</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>A. $y'=\dfrac{1}{x\ln 3}$.</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=3$, ta có $y'=\dfrac{1}{x\ln 3}$.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>p121_q02</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>co_so_trung_binh</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{4} x$ là
 A. $y'=\dfrac{1}{x}$.
@@ -4455,47 +4496,47 @@
 D. $y'=\dfrac{1}{4x}$.</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>B. $y'=\dfrac{1}{x\ln 4}$.</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=4$, ta có $y'=\dfrac{1}{x\ln 4}$.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>p121_q02</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>co_so_trung_binh</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{7} x$ là
 A. $y'=\dfrac{1}{x}$.
@@ -4504,47 +4545,47 @@
 D. $y'=\dfrac{\ln 7}{x}$.</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>C. $y'=\dfrac{1}{x\ln 7}$.</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=7$, ta có $y'=\dfrac{1}{x\ln 7}$.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
         <is>
           <t>p121_q02</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>co_so_lon</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{11} x$ là
 A. $y'=\dfrac{1}{11x}$.
@@ -4553,47 +4594,47 @@
 D. $y'=\dfrac{1}{x\ln 11}$.</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>D. $y'=\dfrac{1}{x\ln 11}$.</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=11$, ta có $y'=\dfrac{1}{x\ln 11}$.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>D18</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>p121_q02</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>co_so_lon</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Trên khoảng $(0;+\infty)$, đạo hàm của hàm số $y=\log_{8} x$ là
 A. $y'=\dfrac{1}{x}$.
@@ -4602,63 +4643,14 @@
 D. $y'=\dfrac{\ln 8}{x}$.</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>C. $y'=\dfrac{1}{x\ln 8}$.</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Áp dụng công thức $(\log_a x)' = \dfrac{1}{x\ln a}$ với $a=8$, ta có $y'=\dfrac{1}{x\ln 8}$.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>D53</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>p124_q21</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>he_so_x_bang_1</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Tập nghiệm của bất phương trình $\log_{2}(x+2)&gt;3$ là
-A. $\left(-\infty;6\right)$.
-B. $\left(4;+\infty\right)$.
-C. $\left(7;+\infty\right)$.
-D. $\left(6;+\infty\right)$.</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>D. $\left(6;+\infty\right)$.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Điều kiện: $x+2&gt;0$. Vì $a=2&gt;1$ nên $\log_{2}(x+2)&gt;3 \Leftrightarrow x+2&gt;2^{3}=8 \Leftrightarrow x&gt;6$. Vậy tập nghiệm là $\left(6;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4683,7 +4675,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>p124_q21</t>
+          <t>p006_q14</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4693,21 +4685,21 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{4}(x+3)&gt;2$ là
-A. $\left(5;+\infty\right)$.
-B. $\left(13;+\infty\right)$.
-C. $\left(-\infty;13\right)$.
-D. $\left(14;+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{2}(x+2)&gt;3$ là
+A. $\left(4;+\infty\right)$.
+B. $\left(7;+\infty\right)$.
+C. $\left(6;+\infty\right)$.
+D. $\left(-\infty;6\right)$.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>B. $\left(13;+\infty\right)$.</t>
+          <t>C. $\left(6;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Điều kiện: $x+3&gt;0$. Vì $a=4&gt;1$ nên $\log_{4}(x+3)&gt;2 \Leftrightarrow x+3&gt;4^{2}=16 \Leftrightarrow x&gt;13$. Vậy tập nghiệm là $\left(13;+\infty\right)$.</t>
+          <t>Điều kiện: $x+2&gt;0$. Vì $a=2&gt;1$ nên $\log_{2}(x+2)&gt;3 \Leftrightarrow x+2&gt;2^{3}=8 \Leftrightarrow x&gt;6$. Vậy tập nghiệm là $\left(6;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4732,31 +4724,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>p124_q21</t>
+          <t>p006_q14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>he_so_x_lon_hon_1</t>
+          <t>he_so_x_bang_1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{5}(3x+4)&gt;0$ là
-A. $\left(-1;+\infty\right)$.
-B. $\left(-3;+\infty\right)$.
-C. $\left(- \dfrac{4}{3};+\infty\right)$.
-D. $\left(-\infty;-1\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{4}(x+3)&gt;2$ là
+A. $\left(13;+\infty\right)$.
+B. $\left(-\infty;13\right)$.
+C. $\left(5;+\infty\right)$.
+D. $\left(14;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>A. $\left(-1;+\infty\right)$.</t>
+          <t>A. $\left(13;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Điều kiện: $3x+4&gt;0$. Vì $a=5&gt;1$ nên $\log_{5}(3x+4)&gt;0 \Leftrightarrow 3x+4&gt;5^{0}=1 \Leftrightarrow x&gt;-1$. Vậy tập nghiệm là $\left(-1;+\infty\right)$.</t>
+          <t>Điều kiện: $x+3&gt;0$. Vì $a=4&gt;1$ nên $\log_{4}(x+3)&gt;2 \Leftrightarrow x+3&gt;4^{2}=16 \Leftrightarrow x&gt;13$. Vậy tập nghiệm là $\left(13;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4781,7 +4773,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>p124_q21</t>
+          <t>p006_q14</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4791,21 +4783,21 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{4}(3x+4)&gt;0$ là
+          <t>Tập nghiệm của bất phương trình $\log_{5}(3x+4)&gt;0$ là
 A. $\left(-3;+\infty\right)$.
 B. $\left(-\infty;-1\right)$.
-C. $\left(- \dfrac{4}{3};+\infty\right)$.
-D. $\left(-1;+\infty\right)$.</t>
+C. $\left(-1;+\infty\right)$.
+D. $\left(- \dfrac{4}{3};+\infty\right)$.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>D. $\left(-1;+\infty\right)$.</t>
+          <t>C. $\left(-1;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Điều kiện: $3x+4&gt;0$. Vì $a=4&gt;1$ nên $\log_{4}(3x+4)&gt;0 \Leftrightarrow 3x+4&gt;4^{0}=1 \Leftrightarrow x&gt;-1$. Vậy tập nghiệm là $\left(-1;+\infty\right)$.</t>
+          <t>Điều kiện: $3x+4&gt;0$. Vì $a=5&gt;1$ nên $\log_{5}(3x+4)&gt;0 \Leftrightarrow 3x+4&gt;5^{0}=1 \Leftrightarrow x&gt;-1$. Vậy tập nghiệm là $\left(-1;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4830,80 +4822,80 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>p124_q21</t>
+          <t>p006_q14</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>he_so_x_lon_hon_1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $\log_{4}(3x+4)&gt;0$ là
+A. $\left(- \dfrac{4}{3};+\infty\right)$.
+B. $\left(-3;+\infty\right)$.
+C. $\left(-1;+\infty\right)$.
+D. $\left(-\infty;-1\right)$.</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>C. $\left(-1;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Điều kiện: $3x+4&gt;0$. Vì $a=4&gt;1$ nên $\log_{4}(3x+4)&gt;0 \Leftrightarrow 3x+4&gt;4^{0}=1 \Leftrightarrow x&gt;-1$. Vậy tập nghiệm là $\left(-1;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>p006_q14</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>dap_so_phan_so</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>Tập nghiệm của bất phương trình $\log_{7}(3x+3)&gt;2$ là
 A. $\left(46;+\infty\right)$.
 B. $\left(\dfrac{46}{3};+\infty\right)$.
-C. $\left(-\infty;\dfrac{46}{3}\right)$.
-D. $\left(\dfrac{11}{3};+\infty\right)$.</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+C. $\left(\dfrac{11}{3};+\infty\right)$.
+D. $\left(-\infty;\dfrac{46}{3}\right)$.</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>B. $\left(\dfrac{46}{3};+\infty\right)$.</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>Điều kiện: $3x+3&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(3x+3)&gt;2 \Leftrightarrow 3x+3&gt;7^{2}=49 \Leftrightarrow x&gt;\dfrac{46}{3}$. Vậy tập nghiệm là $\left(\dfrac{46}{3};+\infty\right)$.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>D53</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Nhân bản</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>p124_q21</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>dap_so_phan_so</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Tập nghiệm của bất phương trình $\log_{2}(2x-6)&gt;0$ là
-A. $\left(-\infty;\dfrac{7}{2}\right)$.
-B. $\left(3;+\infty\right)$.
-C. $\left(\dfrac{7}{2};+\infty\right)$.
-D. $\left(7;+\infty\right)$.</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>C. $\left(\dfrac{7}{2};+\infty\right)$.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Điều kiện: $2x-6&gt;0$. Vì $a=2&gt;1$ nên $\log_{2}(2x-6)&gt;0 \Leftrightarrow 2x-6&gt;2^{0}=1 \Leftrightarrow x&gt;\dfrac{7}{2}$. Vậy tập nghiệm là $\left(\dfrac{7}{2};+\infty\right)$.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4928,31 +4920,31 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>p221_q08</t>
+          <t>p006_q14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>he_so_x_bang_1</t>
+          <t>dap_so_phan_so</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{5}(x+1)&gt;3$ là
-A. $\left(14;+\infty\right)$.
-B. $\left(-\infty;124\right)$.
-C. $\left(125;+\infty\right)$.
-D. $\left(124;+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{2}(2x-6)&gt;0$ là
+A. $\left(-\infty;\dfrac{7}{2}\right)$.
+B. $\left(\dfrac{7}{2};+\infty\right)$.
+C. $\left(7;+\infty\right)$.
+D. $\left(3;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>D. $\left(124;+\infty\right)$.</t>
+          <t>B. $\left(\dfrac{7}{2};+\infty\right)$.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Điều kiện: $x+1&gt;0$. Vì $a=5&gt;1$ nên $\log_{5}(x+1)&gt;3 \Leftrightarrow x+1&gt;5^{3}=125 \Leftrightarrow x&gt;124$. Vậy tập nghiệm là $\left(124;+\infty\right)$.</t>
+          <t>Điều kiện: $2x-6&gt;0$. Vì $a=2&gt;1$ nên $\log_{2}(2x-6)&gt;0 \Leftrightarrow 2x-6&gt;2^{0}=1 \Leftrightarrow x&gt;\dfrac{7}{2}$. Vậy tập nghiệm là $\left(\dfrac{7}{2};+\infty\right)$.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4977,7 +4969,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>p221_q08</t>
+          <t>p124_q21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4987,21 +4979,21 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{5}(x-6)&gt;3$ là
-A. $\left(21;+\infty\right)$.
-B. $\left(-\infty;131\right)$.
-C. $\left(132;+\infty\right)$.
-D. $\left(131;+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{5}(x+1)&gt;3$ là
+A. $\left(-\infty;124\right)$.
+B. $\left(14;+\infty\right)$.
+C. $\left(124;+\infty\right)$.
+D. $\left(125;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>D. $\left(131;+\infty\right)$.</t>
+          <t>C. $\left(124;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Điều kiện: $x-6&gt;0$. Vì $a=5&gt;1$ nên $\log_{5}(x-6)&gt;3 \Leftrightarrow x-6&gt;5^{3}=125 \Leftrightarrow x&gt;131$. Vậy tập nghiệm là $\left(131;+\infty\right)$.</t>
+          <t>Điều kiện: $x+1&gt;0$. Vì $a=5&gt;1$ nên $\log_{5}(x+1)&gt;3 \Leftrightarrow x+1&gt;5^{3}=125 \Leftrightarrow x&gt;124$. Vậy tập nghiệm là $\left(124;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5026,31 +5018,31 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>p221_q08</t>
+          <t>p124_q21</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>he_so_x_lon_hon_1</t>
+          <t>he_so_x_bang_1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{3}(2x+3)&gt;1$ là
-A. $\left(1;+\infty\right)$.
-B. $\left(2;+\infty\right)$.
-C. $\left(0;+\infty\right)$.
-D. $\left(-\infty;0\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{5}(x-6)&gt;3$ là
+A. $\left(131;+\infty\right)$.
+B. $\left(132;+\infty\right)$.
+C. $\left(-\infty;131\right)$.
+D. $\left(21;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C. $\left(0;+\infty\right)$.</t>
+          <t>A. $\left(131;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Điều kiện: $2x+3&gt;0$. Vì $a=3&gt;1$ nên $\log_{3}(2x+3)&gt;1 \Leftrightarrow 2x+3&gt;3^{1}=3 \Leftrightarrow x&gt;0$. Vậy tập nghiệm là $\left(0;+\infty\right)$.</t>
+          <t>Điều kiện: $x-6&gt;0$. Vì $a=5&gt;1$ nên $\log_{5}(x-6)&gt;3 \Leftrightarrow x-6&gt;5^{3}=125 \Leftrightarrow x&gt;131$. Vậy tập nghiệm là $\left(131;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5075,7 +5067,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>p221_q08</t>
+          <t>p124_q21</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5085,21 +5077,21 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{6}(2x+6)&gt;1$ là
-A. $\left(-\infty;0\right)$.
-B. $\left(0;+\infty\right)$.
-C. $\left(1;+\infty\right)$.
-D. $\left(2;+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{3}(2x+3)&gt;1$ là
+A. $\left(2;+\infty\right)$.
+B. $\left(1;+\infty\right)$.
+C. $\left(0;+\infty\right)$.
+D. $\left(-\infty;0\right)$.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>B. $\left(0;+\infty\right)$.</t>
+          <t>C. $\left(0;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Điều kiện: $2x+6&gt;0$. Vì $a=6&gt;1$ nên $\log_{6}(2x+6)&gt;1 \Leftrightarrow 2x+6&gt;6^{1}=6 \Leftrightarrow x&gt;0$. Vậy tập nghiệm là $\left(0;+\infty\right)$.</t>
+          <t>Điều kiện: $2x+3&gt;0$. Vì $a=3&gt;1$ nên $\log_{3}(2x+3)&gt;1 \Leftrightarrow 2x+3&gt;3^{1}=3 \Leftrightarrow x&gt;0$. Vậy tập nghiệm là $\left(0;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5124,31 +5116,31 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>p221_q08</t>
+          <t>p124_q21</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>dap_so_phan_so</t>
+          <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{3}(2x-6)&gt;1$ là
-A. $\left(-\infty;\dfrac{9}{2}\right)$.
-B. $\left(9;+\infty\right)$.
-C. $\left(\dfrac{9}{2};+\infty\right)$.
-D. $\left(\dfrac{11}{2};+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{6}(2x+6)&gt;1$ là
+A. $\left(1;+\infty\right)$.
+B. $\left(2;+\infty\right)$.
+C. $\left(-\infty;0\right)$.
+D. $\left(0;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C. $\left(\dfrac{9}{2};+\infty\right)$.</t>
+          <t>D. $\left(0;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Điều kiện: $2x-6&gt;0$. Vì $a=3&gt;1$ nên $\log_{3}(2x-6)&gt;1 \Leftrightarrow 2x-6&gt;3^{1}=3 \Leftrightarrow x&gt;\dfrac{9}{2}$. Vậy tập nghiệm là $\left(\dfrac{9}{2};+\infty\right)$.</t>
+          <t>Điều kiện: $2x+6&gt;0$. Vì $a=6&gt;1$ nên $\log_{6}(2x+6)&gt;1 \Leftrightarrow 2x+6&gt;6^{1}=6 \Leftrightarrow x&gt;0$. Vậy tập nghiệm là $\left(0;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5173,7 +5165,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>p221_q08</t>
+          <t>p124_q21</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5183,21 +5175,21 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{7}(2x-4)&gt;3$ là
-A. $\left(\dfrac{25}{2};+\infty\right)$.
-B. $\left(-\infty;\dfrac{347}{2}\right)$.
-C. $\left(347;+\infty\right)$.
-D. $\left(\dfrac{347}{2};+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{3}(2x-6)&gt;1$ là
+A. $\left(9;+\infty\right)$.
+B. $\left(\dfrac{9}{2};+\infty\right)$.
+C. $\left(\dfrac{11}{2};+\infty\right)$.
+D. $\left(-\infty;\dfrac{9}{2}\right)$.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>D. $\left(\dfrac{347}{2};+\infty\right)$.</t>
+          <t>B. $\left(\dfrac{9}{2};+\infty\right)$.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Điều kiện: $2x-4&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(2x-4)&gt;3 \Leftrightarrow 2x-4&gt;7^{3}=343 \Leftrightarrow x&gt;\dfrac{347}{2}$. Vậy tập nghiệm là $\left(\dfrac{347}{2};+\infty\right)$.</t>
+          <t>Điều kiện: $2x-6&gt;0$. Vì $a=3&gt;1$ nên $\log_{3}(2x-6)&gt;1 \Leftrightarrow 2x-6&gt;3^{1}=3 \Leftrightarrow x&gt;\dfrac{9}{2}$. Vậy tập nghiệm là $\left(\dfrac{9}{2};+\infty\right)$.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5222,31 +5214,31 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>p236_q12</t>
+          <t>p124_q21</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>he_so_x_bang_1</t>
+          <t>dap_so_phan_so</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{6}(x+3)&gt;3$ là
-A. $\left(213;+\infty\right)$.
-B. $\left(214;+\infty\right)$.
-C. $\left(-\infty;213\right)$.
-D. $\left(15;+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{7}(2x-4)&gt;3$ là
+A. $\left(\dfrac{347}{2};+\infty\right)$.
+B. $\left(\dfrac{25}{2};+\infty\right)$.
+C. $\left(347;+\infty\right)$.
+D. $\left(-\infty;\dfrac{347}{2}\right)$.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>A. $\left(213;+\infty\right)$.</t>
+          <t>A. $\left(\dfrac{347}{2};+\infty\right)$.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Điều kiện: $x+3&gt;0$. Vì $a=6&gt;1$ nên $\log_{6}(x+3)&gt;3 \Leftrightarrow x+3&gt;6^{3}=216 \Leftrightarrow x&gt;213$. Vậy tập nghiệm là $\left(213;+\infty\right)$.</t>
+          <t>Điều kiện: $2x-4&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(2x-4)&gt;3 \Leftrightarrow 2x-4&gt;7^{3}=343 \Leftrightarrow x&gt;\dfrac{347}{2}$. Vậy tập nghiệm là $\left(\dfrac{347}{2};+\infty\right)$.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5271,7 +5263,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>p236_q12</t>
+          <t>p221_q08</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5281,21 +5273,21 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{7}(x+5)&gt;1$ là
-A. $\left(3;+\infty\right)$.
-B. $\left(2;+\infty\right)$.
-C. $\left(-\infty;2\right)$.
-D. $\left(4;+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{6}(x+3)&gt;3$ là
+A. $\left(213;+\infty\right)$.
+B. $\left(-\infty;213\right)$.
+C. $\left(214;+\infty\right)$.
+D. $\left(15;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>B. $\left(2;+\infty\right)$.</t>
+          <t>A. $\left(213;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Điều kiện: $x+5&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(x+5)&gt;1 \Leftrightarrow x+5&gt;7^{1}=7 \Leftrightarrow x&gt;2$. Vậy tập nghiệm là $\left(2;+\infty\right)$.</t>
+          <t>Điều kiện: $x+3&gt;0$. Vì $a=6&gt;1$ nên $\log_{6}(x+3)&gt;3 \Leftrightarrow x+3&gt;6^{3}=216 \Leftrightarrow x&gt;213$. Vậy tập nghiệm là $\left(213;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5320,31 +5312,31 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>p236_q12</t>
+          <t>p221_q08</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>he_so_x_lon_hon_1</t>
+          <t>he_so_x_bang_1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{7}(3x-5)&gt;1$ là
-A. $\left(4;+\infty\right)$.
-B. $\left(-\infty;4\right)$.
-C. $\left(5;+\infty\right)$.
-D. $\left(12;+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{7}(x+5)&gt;1$ là
+A. $\left(-\infty;2\right)$.
+B. $\left(3;+\infty\right)$.
+C. $\left(2;+\infty\right)$.
+D. $\left(4;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>A. $\left(4;+\infty\right)$.</t>
+          <t>C. $\left(2;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Điều kiện: $3x-5&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(3x-5)&gt;1 \Leftrightarrow 3x-5&gt;7^{1}=7 \Leftrightarrow x&gt;4$. Vậy tập nghiệm là $\left(4;+\infty\right)$.</t>
+          <t>Điều kiện: $x+5&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(x+5)&gt;1 \Leftrightarrow x+5&gt;7^{1}=7 \Leftrightarrow x&gt;2$. Vậy tập nghiệm là $\left(2;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5369,7 +5361,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>p236_q12</t>
+          <t>p221_q08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5379,21 +5371,21 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{3}(2x+5)&gt;0$ là
-A. $\left(- \dfrac{5}{2};+\infty\right)$.
-B. $\left(-2;+\infty\right)$.
-C. $\left(-4;+\infty\right)$.
-D. $\left(-\infty;-2\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{7}(3x-5)&gt;1$ là
+A. $\left(-\infty;4\right)$.
+B. $\left(4;+\infty\right)$.
+C. $\left(5;+\infty\right)$.
+D. $\left(12;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>B. $\left(-2;+\infty\right)$.</t>
+          <t>B. $\left(4;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Điều kiện: $2x+5&gt;0$. Vì $a=3&gt;1$ nên $\log_{3}(2x+5)&gt;0 \Leftrightarrow 2x+5&gt;3^{0}=1 \Leftrightarrow x&gt;-2$. Vậy tập nghiệm là $\left(-2;+\infty\right)$.</t>
+          <t>Điều kiện: $3x-5&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(3x-5)&gt;1 \Leftrightarrow 3x-5&gt;7^{1}=7 \Leftrightarrow x&gt;4$. Vậy tập nghiệm là $\left(4;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5418,31 +5410,31 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>p236_q12</t>
+          <t>p221_q08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>dap_so_phan_so</t>
+          <t>he_so_x_lon_hon_1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tập nghiệm của bất phương trình $\log_{6}(3x-2)&gt;1$ là
-A. $\left(\dfrac{11}{3};+\infty\right)$.
-B. $\left(-\infty;\dfrac{8}{3}\right)$.
-C. $\left(8;+\infty\right)$.
-D. $\left(\dfrac{8}{3};+\infty\right)$.</t>
+          <t>Tập nghiệm của bất phương trình $\log_{3}(2x+5)&gt;0$ là
+A. $\left(-4;+\infty\right)$.
+B. $\left(- \dfrac{5}{2};+\infty\right)$.
+C. $\left(-\infty;-2\right)$.
+D. $\left(-2;+\infty\right)$.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>D. $\left(\dfrac{8}{3};+\infty\right)$.</t>
+          <t>D. $\left(-2;+\infty\right)$.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Điều kiện: $3x-2&gt;0$. Vì $a=6&gt;1$ nên $\log_{6}(3x-2)&gt;1 \Leftrightarrow 3x-2&gt;6^{1}=6 \Leftrightarrow x&gt;\dfrac{8}{3}$. Vậy tập nghiệm là $\left(\dfrac{8}{3};+\infty\right)$.</t>
+          <t>Điều kiện: $2x+5&gt;0$. Vì $a=3&gt;1$ nên $\log_{3}(2x+5)&gt;0 \Leftrightarrow 2x+5&gt;3^{0}=1 \Leftrightarrow x&gt;-2$. Vậy tập nghiệm là $\left(-2;+\infty\right)$.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5467,7 +5459,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>p236_q12</t>
+          <t>p221_q08</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5477,24 +5469,367 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
+          <t>Tập nghiệm của bất phương trình $\log_{6}(3x-2)&gt;1$ là
+A. $\left(\dfrac{11}{3};+\infty\right)$.
+B. $\left(8;+\infty\right)$.
+C. $\left(-\infty;\dfrac{8}{3}\right)$.
+D. $\left(\dfrac{8}{3};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>D. $\left(\dfrac{8}{3};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Điều kiện: $3x-2&gt;0$. Vì $a=6&gt;1$ nên $\log_{6}(3x-2)&gt;1 \Leftrightarrow 3x-2&gt;6^{1}=6 \Leftrightarrow x&gt;\dfrac{8}{3}$. Vậy tập nghiệm là $\left(\dfrac{8}{3};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>p221_q08</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>dap_so_phan_so</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
           <t>Tập nghiệm của bất phương trình $\log_{7}(3x+5)&gt;0$ là
-A. $\left(- \dfrac{4}{3};+\infty\right)$.
-B. $\left(- \dfrac{5}{3};+\infty\right)$.
+A. $\left(- \dfrac{5}{3};+\infty\right)$.
+B. $\left(- \dfrac{4}{3};+\infty\right)$.
 C. $\left(-4;+\infty\right)$.
 D. $\left(-\infty;- \dfrac{4}{3}\right)$.</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>A. $\left(- \dfrac{4}{3};+\infty\right)$.</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>B. $\left(- \dfrac{4}{3};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>Điều kiện: $3x+5&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(3x+5)&gt;0 \Leftrightarrow 3x+5&gt;7^{0}=1 \Leftrightarrow x&gt;- \dfrac{4}{3}$. Vậy tập nghiệm là $\left(- \dfrac{4}{3};+\infty\right)$.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>p236_q12</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>he_so_x_bang_1</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $\log_{4}(x-2)&gt;0$ là
+A. $\left(-\infty;3\right)$.
+B. $\left(2;+\infty\right)$.
+C. $\left(4;+\infty\right)$.
+D. $\left(3;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>D. $\left(3;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Điều kiện: $x-2&gt;0$. Vì $a=4&gt;1$ nên $\log_{4}(x-2)&gt;0 \Leftrightarrow x-2&gt;4^{0}=1 \Leftrightarrow x&gt;3$. Vậy tập nghiệm là $\left(3;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>p236_q12</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>he_so_x_bang_1</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $\log_{2}(x-3)&gt;0$ là
+A. $\left(-\infty;4\right)$.
+B. $\left(4;+\infty\right)$.
+C. $\left(3;+\infty\right)$.
+D. $\left(5;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>B. $\left(4;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Điều kiện: $x-3&gt;0$. Vì $a=2&gt;1$ nên $\log_{2}(x-3)&gt;0 \Leftrightarrow x-3&gt;2^{0}=1 \Leftrightarrow x&gt;4$. Vậy tập nghiệm là $\left(4;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>p236_q12</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>he_so_x_lon_hon_1</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $\log_{6}(2x+2)&gt;2$ là
+A. $\left(5;+\infty\right)$.
+B. $\left(34;+\infty\right)$.
+C. $\left(17;+\infty\right)$.
+D. $\left(-\infty;17\right)$.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>C. $\left(17;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Điều kiện: $2x+2&gt;0$. Vì $a=6&gt;1$ nên $\log_{6}(2x+2)&gt;2 \Leftrightarrow 2x+2&gt;6^{2}=36 \Leftrightarrow x&gt;17$. Vậy tập nghiệm là $\left(17;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>p236_q12</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>he_so_x_lon_hon_1</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $\log_{5}(2x-3)&gt;1$ là
+A. $\left(5;+\infty\right)$.
+B. $\left(4;+\infty\right)$.
+C. $\left(8;+\infty\right)$.
+D. $\left(-\infty;4\right)$.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>B. $\left(4;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Điều kiện: $2x-3&gt;0$. Vì $a=5&gt;1$ nên $\log_{5}(2x-3)&gt;1 \Leftrightarrow 2x-3&gt;5^{1}=5 \Leftrightarrow x&gt;4$. Vậy tập nghiệm là $\left(4;+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>p236_q12</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>dap_so_phan_so</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $\log_{2}(2x+1)&gt;1$ là
+A. $\left(1;+\infty\right)$.
+B. $\left(\dfrac{3}{2};+\infty\right)$.
+C. $\left(-\infty;\dfrac{1}{2}\right)$.
+D. $\left(\dfrac{1}{2};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>D. $\left(\dfrac{1}{2};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Điều kiện: $2x+1&gt;0$. Vì $a=2&gt;1$ nên $\log_{2}(2x+1)&gt;1 \Leftrightarrow 2x+1&gt;2^{1}=2 \Leftrightarrow x&gt;\dfrac{1}{2}$. Vậy tập nghiệm là $\left(\dfrac{1}{2};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Đạt</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D53</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Nhân bản</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>p236_q12</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>dap_so_phan_so</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tập nghiệm của bất phương trình $\log_{7}(3x+3)&gt;1$ là
+A. $\left(4;+\infty\right)$.
+B. $\left(-\infty;\dfrac{4}{3}\right)$.
+C. $\left(\dfrac{4}{3};+\infty\right)$.
+D. $\left(\dfrac{7}{3};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>C. $\left(\dfrac{4}{3};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Điều kiện: $3x+3&gt;0$. Vì $a=7&gt;1$ nên $\log_{7}(3x+3)&gt;1 \Leftrightarrow 3x+3&gt;7^{1}=7 \Leftrightarrow x&gt;\dfrac{4}{3}$. Vậy tập nghiệm là $\left(\dfrac{4}{3};+\infty\right)$.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
         <is>
           <t>Đạt</t>
         </is>
